--- a/03_Group_comparisons/Proteome/03_Set_Contrasts/T2/c_data/set_contrasts.xlsx
+++ b/03_Group_comparisons/Proteome/03_Set_Contrasts/T2/c_data/set_contrasts.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13051" uniqueCount="3638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13081" uniqueCount="3656">
   <si>
     <t>sheet</t>
   </si>
@@ -10472,7 +10472,7 @@
     <t>fit</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/03_Protein_Contrasts/T2/c_data/fit.rds</t>
+    <t>03_Group_comparisons/Proteome/02_Protein_Contrasts/T2/c_data/fit.rds</t>
   </si>
   <si>
     <t>3202a5435a20130b881f51bf010d4f74</t>
@@ -10481,7 +10481,7 @@
     <t>design</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/02_Design_Contrasts/T2/c_data/design.rds</t>
+    <t>03_Group_comparisons/Proteome/01_Design_Contrasts/T2/c_data/design.rds</t>
   </si>
   <si>
     <t>ec109143c9337576f3039e2d1550a7c0</t>
@@ -10505,7 +10505,7 @@
     <t>phenotype</t>
   </si>
   <si>
-    <t>00_Input/phenotype.csv</t>
+    <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
     <t>5a1989db406daa0b70189a9f0df52cf3</t>
@@ -10634,12 +10634,21 @@
     <t>Github (Dustyn-T-Lewis/enrichVolcano@d3fed631f4ae95e01bd61137699313f8de5cc86e)</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
     <t>fastmatch</t>
   </si>
   <si>
@@ -10700,6 +10709,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -10712,6 +10733,18 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -10727,9 +10760,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -10754,6 +10784,12 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
     <t>pillar</t>
   </si>
   <si>
@@ -10838,6 +10874,12 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -10913,6 +10955,12 @@
     <t>0.5.0</t>
   </si>
   <si>
+    <t>utf8</t>
+  </si>
+  <si>
+    <t>1.2.6</t>
+  </si>
+  <si>
     <t>vctrs</t>
   </si>
   <si>
@@ -10931,10 +10979,16 @@
     <t>3.0.2</t>
   </si>
   <si>
-    <t>writexl</t>
-  </si>
-  <si>
-    <t>2.0.1</t>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -86545,7 +86599,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -86792,13 +86846,13 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>3541</v>
       </c>
       <c r="B23" t="s">
-        <v>3541</v>
+        <v>3523</v>
       </c>
       <c r="C23" t="s">
-        <v>3498</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -86814,21 +86868,21 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" t="s">
         <v>3544</v>
       </c>
-      <c r="B25" t="s">
-        <v>3545</v>
-      </c>
       <c r="C25" t="s">
-        <v>3501</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>3545</v>
+      </c>
+      <c r="B26" t="s">
         <v>3546</v>
-      </c>
-      <c r="B26" t="s">
-        <v>3547</v>
       </c>
       <c r="C26" t="s">
         <v>3501</v>
@@ -86836,10 +86890,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
+        <v>3547</v>
+      </c>
+      <c r="B27" t="s">
         <v>3548</v>
-      </c>
-      <c r="B27" t="s">
-        <v>3549</v>
       </c>
       <c r="C27" t="s">
         <v>3501</v>
@@ -86847,10 +86901,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>3549</v>
+      </c>
+      <c r="B28" t="s">
         <v>3550</v>
-      </c>
-      <c r="B28" t="s">
-        <v>3545</v>
       </c>
       <c r="C28" t="s">
         <v>3501</v>
@@ -86872,7 +86926,7 @@
         <v>3553</v>
       </c>
       <c r="B30" t="s">
-        <v>3554</v>
+        <v>3548</v>
       </c>
       <c r="C30" t="s">
         <v>3501</v>
@@ -86880,10 +86934,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>3554</v>
+      </c>
+      <c r="B31" t="s">
         <v>3555</v>
-      </c>
-      <c r="B31" t="s">
-        <v>3556</v>
       </c>
       <c r="C31" t="s">
         <v>3501</v>
@@ -86891,10 +86945,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>3556</v>
+      </c>
+      <c r="B32" t="s">
         <v>3557</v>
-      </c>
-      <c r="B32" t="s">
-        <v>3558</v>
       </c>
       <c r="C32" t="s">
         <v>3501</v>
@@ -86902,21 +86956,21 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>3558</v>
+      </c>
+      <c r="B33" t="s">
         <v>3559</v>
       </c>
-      <c r="B33" t="s">
-        <v>3560</v>
-      </c>
       <c r="C33" t="s">
-        <v>3498</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>3560</v>
+      </c>
+      <c r="B34" t="s">
         <v>3561</v>
-      </c>
-      <c r="B34" t="s">
-        <v>3562</v>
       </c>
       <c r="C34" t="s">
         <v>3501</v>
@@ -86924,10 +86978,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>3562</v>
+      </c>
+      <c r="B35" t="s">
         <v>3563</v>
-      </c>
-      <c r="B35" t="s">
-        <v>3564</v>
       </c>
       <c r="C35" t="s">
         <v>3501</v>
@@ -86935,10 +86989,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>3564</v>
+      </c>
+      <c r="B36" t="s">
         <v>3565</v>
-      </c>
-      <c r="B36" t="s">
-        <v>3566</v>
       </c>
       <c r="C36" t="s">
         <v>3501</v>
@@ -86946,32 +87000,32 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>3566</v>
+      </c>
+      <c r="B37" t="s">
         <v>3567</v>
       </c>
-      <c r="B37" t="s">
-        <v>3568</v>
-      </c>
       <c r="C37" t="s">
-        <v>3501</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>3568</v>
+      </c>
+      <c r="B38" t="s">
         <v>3569</v>
       </c>
-      <c r="B38" t="s">
-        <v>3570</v>
-      </c>
       <c r="C38" t="s">
-        <v>3498</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>3570</v>
+      </c>
+      <c r="B39" t="s">
         <v>3571</v>
-      </c>
-      <c r="B39" t="s">
-        <v>3572</v>
       </c>
       <c r="C39" t="s">
         <v>3501</v>
@@ -86979,10 +87033,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>3572</v>
+      </c>
+      <c r="B40" t="s">
         <v>3573</v>
-      </c>
-      <c r="B40" t="s">
-        <v>3574</v>
       </c>
       <c r="C40" t="s">
         <v>3501</v>
@@ -86990,10 +87044,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>3574</v>
+      </c>
+      <c r="B41" t="s">
         <v>3575</v>
-      </c>
-      <c r="B41" t="s">
-        <v>3576</v>
       </c>
       <c r="C41" t="s">
         <v>3501</v>
@@ -87001,10 +87055,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>3576</v>
+      </c>
+      <c r="B42" t="s">
         <v>3577</v>
-      </c>
-      <c r="B42" t="s">
-        <v>3578</v>
       </c>
       <c r="C42" t="s">
         <v>3501</v>
@@ -87012,10 +87066,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="B43" t="s">
-        <v>3580</v>
+        <v>3538</v>
       </c>
       <c r="C43" t="s">
         <v>3501</v>
@@ -87023,21 +87077,21 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>3581</v>
+        <v>3579</v>
       </c>
       <c r="B44" t="s">
-        <v>3582</v>
+        <v>3580</v>
       </c>
       <c r="C44" t="s">
-        <v>3501</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>3583</v>
+        <v>3581</v>
       </c>
       <c r="B45" t="s">
-        <v>3584</v>
+        <v>3582</v>
       </c>
       <c r="C45" t="s">
         <v>3501</v>
@@ -87045,10 +87099,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>3585</v>
+        <v>3583</v>
       </c>
       <c r="B46" t="s">
-        <v>3586</v>
+        <v>3584</v>
       </c>
       <c r="C46" t="s">
         <v>3501</v>
@@ -87056,21 +87110,21 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>3585</v>
       </c>
       <c r="B47" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="C47" t="s">
-        <v>3498</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>3587</v>
+      </c>
+      <c r="B48" t="s">
         <v>3588</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3589</v>
       </c>
       <c r="C48" t="s">
         <v>3501</v>
@@ -87078,10 +87132,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>3589</v>
+      </c>
+      <c r="B49" t="s">
         <v>3590</v>
-      </c>
-      <c r="B49" t="s">
-        <v>3591</v>
       </c>
       <c r="C49" t="s">
         <v>3501</v>
@@ -87089,10 +87143,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>3591</v>
+      </c>
+      <c r="B50" t="s">
         <v>3592</v>
-      </c>
-      <c r="B50" t="s">
-        <v>3593</v>
       </c>
       <c r="C50" t="s">
         <v>3501</v>
@@ -87100,10 +87154,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>3593</v>
+      </c>
+      <c r="B51" t="s">
         <v>3594</v>
-      </c>
-      <c r="B51" t="s">
-        <v>3595</v>
       </c>
       <c r="C51" t="s">
         <v>3501</v>
@@ -87111,10 +87165,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>3595</v>
+      </c>
+      <c r="B52" t="s">
         <v>3596</v>
-      </c>
-      <c r="B52" t="s">
-        <v>3597</v>
       </c>
       <c r="C52" t="s">
         <v>3501</v>
@@ -87122,10 +87176,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>3597</v>
+      </c>
+      <c r="B53" t="s">
         <v>3598</v>
-      </c>
-      <c r="B53" t="s">
-        <v>3599</v>
       </c>
       <c r="C53" t="s">
         <v>3501</v>
@@ -87133,32 +87187,32 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>3600</v>
+        <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>3601</v>
+        <v>3599</v>
       </c>
       <c r="C54" t="s">
-        <v>3501</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>3602</v>
+        <v>3600</v>
       </c>
       <c r="B55" t="s">
-        <v>3603</v>
+        <v>3601</v>
       </c>
       <c r="C55" t="s">
-        <v>3604</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>3605</v>
+        <v>3602</v>
       </c>
       <c r="B56" t="s">
-        <v>3606</v>
+        <v>3603</v>
       </c>
       <c r="C56" t="s">
         <v>3501</v>
@@ -87166,21 +87220,21 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>3607</v>
+        <v>3604</v>
       </c>
       <c r="B57" t="s">
-        <v>3608</v>
+        <v>3605</v>
       </c>
       <c r="C57" t="s">
-        <v>3498</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>3609</v>
+        <v>3606</v>
       </c>
       <c r="B58" t="s">
-        <v>3610</v>
+        <v>3607</v>
       </c>
       <c r="C58" t="s">
         <v>3501</v>
@@ -87188,10 +87242,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>3611</v>
+        <v>3608</v>
       </c>
       <c r="B59" t="s">
-        <v>3612</v>
+        <v>3609</v>
       </c>
       <c r="C59" t="s">
         <v>3501</v>
@@ -87199,10 +87253,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>3613</v>
+        <v>3610</v>
       </c>
       <c r="B60" t="s">
-        <v>3614</v>
+        <v>3611</v>
       </c>
       <c r="C60" t="s">
         <v>3501</v>
@@ -87210,10 +87264,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>3615</v>
+        <v>3612</v>
       </c>
       <c r="B61" t="s">
-        <v>3616</v>
+        <v>3613</v>
       </c>
       <c r="C61" t="s">
         <v>3501</v>
@@ -87221,21 +87275,21 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>3617</v>
+        <v>3614</v>
       </c>
       <c r="B62" t="s">
-        <v>3618</v>
+        <v>3615</v>
       </c>
       <c r="C62" t="s">
-        <v>3501</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>3619</v>
+        <v>3617</v>
       </c>
       <c r="B63" t="s">
-        <v>3620</v>
+        <v>3618</v>
       </c>
       <c r="C63" t="s">
         <v>3501</v>
@@ -87243,10 +87297,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>3621</v>
+        <v>3619</v>
       </c>
       <c r="B64" t="s">
-        <v>3622</v>
+        <v>3620</v>
       </c>
       <c r="C64" t="s">
         <v>3501</v>
@@ -87254,21 +87308,21 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>3623</v>
+        <v>3621</v>
       </c>
       <c r="B65" t="s">
-        <v>3624</v>
+        <v>3622</v>
       </c>
       <c r="C65" t="s">
-        <v>3501</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>3625</v>
+        <v>3623</v>
       </c>
       <c r="B66" t="s">
-        <v>3626</v>
+        <v>3624</v>
       </c>
       <c r="C66" t="s">
         <v>3501</v>
@@ -87276,10 +87330,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>3627</v>
+        <v>3625</v>
       </c>
       <c r="B67" t="s">
-        <v>3533</v>
+        <v>3626</v>
       </c>
       <c r="C67" t="s">
         <v>3501</v>
@@ -87287,10 +87341,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>3627</v>
+      </c>
+      <c r="B68" t="s">
         <v>3628</v>
-      </c>
-      <c r="B68" t="s">
-        <v>3629</v>
       </c>
       <c r="C68" t="s">
         <v>3501</v>
@@ -87298,10 +87352,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>3629</v>
+      </c>
+      <c r="B69" t="s">
         <v>3630</v>
-      </c>
-      <c r="B69" t="s">
-        <v>3631</v>
       </c>
       <c r="C69" t="s">
         <v>3501</v>
@@ -87309,10 +87363,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>3631</v>
+      </c>
+      <c r="B70" t="s">
         <v>3632</v>
-      </c>
-      <c r="B70" t="s">
-        <v>3633</v>
       </c>
       <c r="C70" t="s">
         <v>3501</v>
@@ -87320,10 +87374,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>3633</v>
+      </c>
+      <c r="B71" t="s">
         <v>3634</v>
-      </c>
-      <c r="B71" t="s">
-        <v>3635</v>
       </c>
       <c r="C71" t="s">
         <v>3501</v>
@@ -87331,13 +87385,123 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>3635</v>
+      </c>
+      <c r="B72" t="s">
         <v>3636</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
         <v>3637</v>
       </c>
-      <c r="C72" t="s">
-        <v>3604</v>
+      <c r="B73" t="s">
+        <v>3638</v>
+      </c>
+      <c r="C73" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>3639</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3640</v>
+      </c>
+      <c r="C74" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>3641</v>
+      </c>
+      <c r="B75" t="s">
+        <v>3533</v>
+      </c>
+      <c r="C75" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>3642</v>
+      </c>
+      <c r="B76" t="s">
+        <v>3643</v>
+      </c>
+      <c r="C76" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>3644</v>
+      </c>
+      <c r="B77" t="s">
+        <v>3645</v>
+      </c>
+      <c r="C77" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>3646</v>
+      </c>
+      <c r="B78" t="s">
+        <v>3647</v>
+      </c>
+      <c r="C78" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>3648</v>
+      </c>
+      <c r="B79" t="s">
+        <v>3649</v>
+      </c>
+      <c r="C79" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>3650</v>
+      </c>
+      <c r="B80" t="s">
+        <v>3651</v>
+      </c>
+      <c r="C80" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>3652</v>
+      </c>
+      <c r="B81" t="s">
+        <v>3653</v>
+      </c>
+      <c r="C81" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>3654</v>
+      </c>
+      <c r="B82" t="s">
+        <v>3655</v>
+      </c>
+      <c r="C82" t="s">
+        <v>3501</v>
       </c>
     </row>
   </sheetData>
